--- a/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/PreTrdBondInvestTrade001.xlsx
+++ b/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/PreTrdBondInvestTrade001.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BS2.1.2\tams-invest-parent\tams-invest-trade\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workSpaceZhuNew\tams-invest-parent\tams-invest-trade\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -56,10 +56,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>全面总额(万元)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>清算速度</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -113,6 +109,10 @@
   </si>
   <si>
     <t>结算币种</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>券面总额(万元)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -472,12 +472,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="22" width="15.625" customWidth="1"/>
+    <col min="1" max="22" width="15.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -508,50 +508,50 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>23</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
